--- a/research/traditional_assets/database/data/new_zealand/new_zealand_trucking.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_trucking.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0519</v>
+        <v>0.00289</v>
       </c>
       <c r="G2">
-        <v>0.06422018348623854</v>
+        <v>0.08782527881040891</v>
       </c>
       <c r="H2">
-        <v>0.06422018348623854</v>
+        <v>0.08782527881040891</v>
       </c>
       <c r="I2">
-        <v>-0.04680154936752964</v>
+        <v>-0.01311107049102345</v>
       </c>
       <c r="J2">
-        <v>-0.04680154936752964</v>
+        <v>-0.01311107049102345</v>
       </c>
       <c r="K2">
-        <v>-9.550000000000001</v>
+        <v>-0.922</v>
       </c>
       <c r="L2">
-        <v>-0.03809333865177503</v>
+        <v>-0.004284386617100372</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>26.6</v>
+        <v>24.2</v>
       </c>
       <c r="V2">
-        <v>0.08664495114006515</v>
+        <v>0.05155517682147422</v>
       </c>
       <c r="W2">
-        <v>-0.04549785612196284</v>
+        <v>-0.004187102633969119</v>
       </c>
       <c r="X2">
-        <v>0.06195040876949587</v>
+        <v>0.09465315994460144</v>
       </c>
       <c r="Y2">
-        <v>-0.1074482648914587</v>
+        <v>-0.09884026257857056</v>
       </c>
       <c r="Z2">
-        <v>0.7599716139220183</v>
+        <v>0.7483329982299952</v>
       </c>
       <c r="AA2">
-        <v>-0.03556784900689251</v>
+        <v>-0.009811446690552394</v>
       </c>
       <c r="AB2">
-        <v>0.05052033507503283</v>
+        <v>0.08401934390453376</v>
       </c>
       <c r="AC2">
-        <v>-0.08608818408192534</v>
+        <v>-0.09383079059508616</v>
       </c>
       <c r="AD2">
-        <v>115.4</v>
+        <v>112</v>
       </c>
       <c r="AE2">
-        <v>0.0807421321983976</v>
+        <v>0.3725118483412322</v>
       </c>
       <c r="AF2">
-        <v>115.4807421321984</v>
+        <v>112.3725118483412</v>
       </c>
       <c r="AG2">
-        <v>88.88074213219841</v>
+        <v>88.17251184834123</v>
       </c>
       <c r="AH2">
-        <v>0.2733396593401726</v>
+        <v>0.1931554165241051</v>
       </c>
       <c r="AI2">
-        <v>0.3460815310895197</v>
+        <v>0.3525163170336451</v>
       </c>
       <c r="AJ2">
-        <v>0.2245139322854912</v>
+        <v>0.1581364037406564</v>
       </c>
       <c r="AK2">
-        <v>0.289437694839018</v>
+        <v>0.2993236242414101</v>
       </c>
       <c r="AL2">
-        <v>7.6</v>
+        <v>6.68</v>
       </c>
       <c r="AM2">
-        <v>7.571</v>
+        <v>6.669</v>
       </c>
       <c r="AN2">
-        <v>7.130939875177656</v>
+        <v>5.805214326439642</v>
       </c>
       <c r="AO2">
-        <v>-1.552631578947369</v>
+        <v>-0.470059880239521</v>
       </c>
       <c r="AP2">
-        <v>5.492229013915739</v>
+        <v>4.570181508751425</v>
       </c>
       <c r="AQ2">
-        <v>-1.558578787478537</v>
+        <v>-0.470835207677313</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0519</v>
+        <v>0.00289</v>
       </c>
       <c r="G3">
-        <v>0.06422018348623854</v>
+        <v>0.08782527881040891</v>
       </c>
       <c r="H3">
-        <v>0.06422018348623854</v>
+        <v>0.08782527881040891</v>
       </c>
       <c r="I3">
-        <v>-0.04680154936752964</v>
+        <v>-0.01311107049102345</v>
       </c>
       <c r="J3">
-        <v>-0.04680154936752964</v>
+        <v>-0.01311107049102345</v>
       </c>
       <c r="K3">
-        <v>-9.550000000000001</v>
+        <v>-0.922</v>
       </c>
       <c r="L3">
-        <v>-0.03809333865177503</v>
+        <v>-0.004284386617100372</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>26.6</v>
+        <v>24.2</v>
       </c>
       <c r="V3">
-        <v>0.08664495114006515</v>
+        <v>0.05155517682147422</v>
       </c>
       <c r="W3">
-        <v>-0.04549785612196284</v>
+        <v>-0.004187102633969119</v>
       </c>
       <c r="X3">
-        <v>0.06195040876949587</v>
+        <v>0.09465315994460144</v>
       </c>
       <c r="Y3">
-        <v>-0.1074482648914587</v>
+        <v>-0.09884026257857056</v>
       </c>
       <c r="Z3">
-        <v>0.7599716139220183</v>
+        <v>0.7483329982299952</v>
       </c>
       <c r="AA3">
-        <v>-0.03556784900689251</v>
+        <v>-0.009811446690552394</v>
       </c>
       <c r="AB3">
-        <v>0.05052033507503283</v>
+        <v>0.08401934390453376</v>
       </c>
       <c r="AC3">
-        <v>-0.08608818408192534</v>
+        <v>-0.09383079059508616</v>
       </c>
       <c r="AD3">
-        <v>115.4</v>
+        <v>112</v>
       </c>
       <c r="AE3">
-        <v>0.0807421321983976</v>
+        <v>0.3725118483412322</v>
       </c>
       <c r="AF3">
-        <v>115.4807421321984</v>
+        <v>112.3725118483412</v>
       </c>
       <c r="AG3">
-        <v>88.88074213219841</v>
+        <v>88.17251184834123</v>
       </c>
       <c r="AH3">
-        <v>0.2733396593401726</v>
+        <v>0.1931554165241051</v>
       </c>
       <c r="AI3">
-        <v>0.3460815310895197</v>
+        <v>0.3525163170336451</v>
       </c>
       <c r="AJ3">
-        <v>0.2245139322854912</v>
+        <v>0.1581364037406564</v>
       </c>
       <c r="AK3">
-        <v>0.289437694839018</v>
+        <v>0.2993236242414101</v>
       </c>
       <c r="AL3">
-        <v>7.6</v>
+        <v>6.68</v>
       </c>
       <c r="AM3">
-        <v>7.571</v>
+        <v>6.669</v>
       </c>
       <c r="AN3">
-        <v>7.130939875177656</v>
+        <v>5.805214326439642</v>
       </c>
       <c r="AO3">
-        <v>-1.552631578947369</v>
+        <v>-0.470059880239521</v>
       </c>
       <c r="AP3">
-        <v>5.492229013915739</v>
+        <v>4.570181508751425</v>
       </c>
       <c r="AQ3">
-        <v>-1.558578787478537</v>
+        <v>-0.470835207677313</v>
       </c>
     </row>
   </sheetData>
